--- a/Cleaned data set.xlsx
+++ b/Cleaned data set.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA6B0BD-11EE-4127-BE14-1BD74881E6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24425E35-D25A-4591-AD3A-ED51123C3DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="28455" windowHeight="15210" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pivot table" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId4"/>
+    <pivotCache cacheId="10" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -12904,9 +12904,6 @@
     <t>Items in cart</t>
   </si>
   <si>
-    <t>COUNT</t>
-  </si>
-  <si>
     <t>Median</t>
   </si>
   <si>
@@ -12935,14 +12932,18 @@
   </si>
   <si>
     <t>Sum of Quantity</t>
+  </si>
+  <si>
+    <t>Count</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -13019,14 +13020,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="4">
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -13124,7 +13149,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-NG"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -13175,7 +13200,6 @@
               <a:endParaRPr lang="en-NG"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -13232,7 +13256,6 @@
               <a:endParaRPr lang="en-NG"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -13430,7 +13453,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -13750,6 +13772,76 @@
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -13783,6 +13875,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-78E5-4C43-A1EC-7BD95386771D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -13798,6 +13895,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-78E5-4C43-A1EC-7BD95386771D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -13813,6 +13915,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-78E5-4C43-A1EC-7BD95386771D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -13828,6 +13935,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-78E5-4C43-A1EC-7BD95386771D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -13843,6 +13955,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-78E5-4C43-A1EC-7BD95386771D}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -14081,7 +14198,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-NG"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -36689,96 +36806,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B981FC6B-1841-447D-B627-5867778A01E2}" name="PivotTable4" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
-  <location ref="M3:N9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="14">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="2" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="6">
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField dataField="1" numFmtId="2" showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="12"/>
-  </rowFields>
-  <rowItems count="6">
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of TotalPrice" fld="13" baseField="0" baseItem="0" numFmtId="2"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9A5AC0BF-36FC-4737-94D2-94BE00AA479A}" name="PivotTable3" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9A5AC0BF-36FC-4737-94D2-94BE00AA479A}" name="PivotTable3" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="G3:H9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField dataField="1" showAll="0">
@@ -38038,12 +38066,72 @@
   <dataFields count="1">
     <dataField name="Count of OrderID" fld="0" subtotal="count" showDataAs="percentOfTotal" baseField="0" baseItem="0" numFmtId="10"/>
   </dataFields>
-  <chartFormats count="1">
+  <chartFormats count="6">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="8" count="1" selected="0">
+            <x v="4"/>
           </reference>
         </references>
       </pivotArea>
@@ -38061,8 +38149,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4139FA99-124D-4F82-91DF-2ED0366DB05D}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4139FA99-124D-4F82-91DF-2ED0366DB05D}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:C11" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -38174,6 +38262,108 @@
     </ext>
   </extLst>
 </pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B981FC6B-1841-447D-B627-5867778A01E2}" name="PivotTable4" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+  <location ref="M3:N9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="2" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="6">
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="2" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="12"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of TotalPrice" fld="13" baseField="0" baseItem="0" numFmtId="2"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E713A6F3-E433-474E-B458-786C805AC79A}" name="Table1" displayName="Table1" ref="A1:E7" totalsRowShown="0" headerRowDxfId="2">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{1A5C0562-A6D7-49C8-A7B8-C2899BA90A7A}" name="Metric"/>
+    <tableColumn id="2" xr3:uid="{EA0983FA-775F-410D-9A39-51666125E805}" name="Total Price" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{765AB281-9C18-4423-862E-2E54F4AD9DC0}" name="Unit price" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{FA20FF3E-B09D-430D-A2C1-550ABBEDDCC7}" name="Quantity"/>
+    <tableColumn id="5" xr3:uid="{789B636E-6CF7-45BC-8B95-8C304ADE9551}" name="Items in cart"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -38475,25 +38665,25 @@
   <sheetData>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>4294</v>
+        <v>4293</v>
       </c>
       <c r="B3" t="s">
+        <v>4296</v>
+      </c>
+      <c r="C3" t="s">
         <v>4297</v>
       </c>
-      <c r="C3" t="s">
-        <v>4298</v>
-      </c>
       <c r="G3" s="8" t="s">
-        <v>4294</v>
+        <v>4293</v>
       </c>
       <c r="H3" t="s">
+        <v>4295</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>4293</v>
+      </c>
+      <c r="N3" t="s">
         <v>4296</v>
-      </c>
-      <c r="M3" s="8" t="s">
-        <v>4294</v>
-      </c>
-      <c r="N3" t="s">
-        <v>4297</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -38503,13 +38693,13 @@
       <c r="B4" s="3">
         <v>205885.34000000008</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4">
         <v>547</v>
       </c>
       <c r="G4" s="9" t="s">
         <v>3071</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="10">
         <v>0.20833333333333334</v>
       </c>
       <c r="M4" s="9" t="s">
@@ -38526,13 +38716,13 @@
       <c r="B5" s="3">
         <v>185972.69</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5">
         <v>513</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>3073</v>
       </c>
-      <c r="H5" s="11">
+      <c r="H5" s="10">
         <v>0.1925</v>
       </c>
       <c r="M5" s="9" t="s">
@@ -38549,13 +38739,13 @@
       <c r="B6" s="3">
         <v>181261.63</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6">
         <v>502</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>3074</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="10">
         <v>0.19750000000000001</v>
       </c>
       <c r="M6" s="9" t="s">
@@ -38572,13 +38762,13 @@
       <c r="B7" s="3">
         <v>158868.86999999994</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7">
         <v>458</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>3072</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="10">
         <v>0.20583333333333334</v>
       </c>
       <c r="M7" s="9" t="s">
@@ -38595,13 +38785,13 @@
       <c r="B8" s="3">
         <v>165725.76000000001</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8">
         <v>468</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>3070</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="10">
         <v>0.19583333333333333</v>
       </c>
       <c r="M8" s="9" t="s">
@@ -38618,17 +38808,17 @@
       <c r="B9" s="3">
         <v>192807.93</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9">
         <v>533</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>4295</v>
-      </c>
-      <c r="H9" s="11">
+        <v>4294</v>
+      </c>
+      <c r="H9" s="10">
         <v>1</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>4295</v>
+        <v>4294</v>
       </c>
       <c r="N9" s="3">
         <v>1264761.96</v>
@@ -38641,18 +38831,18 @@
       <c r="B10" s="3">
         <v>174239.7399999999</v>
       </c>
-      <c r="C10" s="10">
+      <c r="C10">
         <v>514</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>4295</v>
+        <v>4294</v>
       </c>
       <c r="B11" s="3">
         <v>1264761.96</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11">
         <v>3535</v>
       </c>
     </row>
@@ -91522,7 +91712,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -91532,33 +91722,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4761EE72-EEA0-4CEC-BD8E-5E82419D7599}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="13.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="11" t="s">
         <v>4284</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="11" t="s">
         <v>4285</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>4286</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>4287</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4288</v>
-      </c>
-      <c r="B2">
+        <v>4298</v>
+      </c>
+      <c r="B2" s="12">
         <f>COUNT('Raw cleaned data'!N2:N1201)</f>
         <v>1200</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="12">
         <f>COUNT(('Raw cleaned data'!F2:F1201))</f>
         <v>1200</v>
       </c>
@@ -91573,34 +91767,34 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4290</v>
-      </c>
-      <c r="B3" s="3">
+        <v>4289</v>
+      </c>
+      <c r="B3" s="12">
         <f>AVERAGE('Raw cleaned data'!N2:N1201)</f>
         <v>1053.9683000000005</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="12">
         <f>AVERAGE('Raw cleaned data'!F2:F1201)</f>
         <v>356.41275000000007</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="3">
         <f>AVERAGE('Raw cleaned data'!E2:E1201)</f>
         <v>2.9458333333333333</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="3">
         <f>AVERAGE('Raw cleaned data'!K2:K1201)</f>
         <v>5.4850000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4289</v>
-      </c>
-      <c r="B4" s="3">
+        <v>4288</v>
+      </c>
+      <c r="B4" s="12">
         <f>MEDIAN('Raw cleaned data'!N2:N1201)</f>
         <v>823.61500000000001</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="12">
         <f>MEDIAN('Raw cleaned data'!F2:F1201)</f>
         <v>364.21</v>
       </c>
@@ -91615,13 +91809,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4291</v>
-      </c>
-      <c r="B5" s="3">
+        <v>4290</v>
+      </c>
+      <c r="B5" s="12">
         <f>MIN('Raw cleaned data'!N2:N1201)</f>
         <v>11.39</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="12">
         <f>MIN('Raw cleaned data'!F2:F1201)</f>
         <v>11.39</v>
       </c>
@@ -91636,13 +91830,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4292</v>
-      </c>
-      <c r="B6" s="3">
+        <v>4291</v>
+      </c>
+      <c r="B6" s="12">
         <f>MAX('Raw cleaned data'!N2:N1201)</f>
         <v>3456.4</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="12">
         <f>MAX('Raw cleaned data'!F2:F1201)</f>
         <v>699.93</v>
       </c>
@@ -91657,13 +91851,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4293</v>
-      </c>
-      <c r="B7" s="3">
+        <v>4292</v>
+      </c>
+      <c r="B7" s="12">
         <f>SUM('Raw cleaned data'!N2:N1201)</f>
         <v>1264761.9600000004</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="12">
         <f>SUM('Raw cleaned data'!F2:F1201)</f>
         <v>427695.3000000001</v>
       </c>
@@ -91678,5 +91872,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>